--- a/internal_doc/05.测试设计/可靠性测试/基本操作故障测试/基本操作故障测试设计.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/基本操作故障测试/基本操作故障测试设计.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2310" windowHeight="900" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="2310" windowHeight="900"/>
   </bookViews>
   <sheets>
     <sheet name="g3d3普通表详细设计" sheetId="1" r:id="rId1"/>
@@ -1760,6 +1760,8 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1769,16 +1771,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -2201,7 +2201,7 @@
       <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="62" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -2217,7 +2217,7 @@
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
-      <c r="D4" s="61"/>
+      <c r="D4" s="63"/>
       <c r="E4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2231,7 +2231,7 @@
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
-      <c r="D5" s="61"/>
+      <c r="D5" s="63"/>
       <c r="E5" s="5" t="s">
         <v>199</v>
       </c>
@@ -2243,7 +2243,7 @@
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
-      <c r="D6" s="61"/>
+      <c r="D6" s="63"/>
       <c r="E6" s="11" t="s">
         <v>17</v>
       </c>
@@ -2261,7 +2261,7 @@
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
-      <c r="D7" s="62"/>
+      <c r="D7" s="64"/>
       <c r="E7" s="11" t="s">
         <v>195</v>
       </c>
@@ -2277,7 +2277,7 @@
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="D8" s="62" t="s">
         <v>118</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -2293,7 +2293,7 @@
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
-      <c r="D9" s="61"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="5" t="s">
         <v>19</v>
       </c>
@@ -2307,7 +2307,7 @@
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
-      <c r="D10" s="61"/>
+      <c r="D10" s="63"/>
       <c r="E10" s="5" t="s">
         <v>199</v>
       </c>
@@ -2319,7 +2319,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
-      <c r="D11" s="61"/>
+      <c r="D11" s="63"/>
       <c r="E11" s="11" t="s">
         <v>17</v>
       </c>
@@ -2335,7 +2335,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
-      <c r="D12" s="62"/>
+      <c r="D12" s="64"/>
       <c r="E12" s="11" t="s">
         <v>195</v>
       </c>
@@ -2405,7 +2405,7 @@
       <c r="C16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="68" t="s">
         <v>22</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -2421,7 +2421,7 @@
       <c r="A17" s="4"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
-      <c r="D17" s="64"/>
+      <c r="D17" s="66"/>
       <c r="E17" s="5" t="s">
         <v>196</v>
       </c>
@@ -2433,7 +2433,7 @@
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
-      <c r="D18" s="65"/>
+      <c r="D18" s="67"/>
       <c r="E18" s="11" t="s">
         <v>127</v>
       </c>
@@ -2615,7 +2615,7 @@
       <c r="C30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D30" s="60" t="s">
+      <c r="D30" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="5" t="s">
@@ -2631,7 +2631,7 @@
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
-      <c r="D31" s="61"/>
+      <c r="D31" s="63"/>
       <c r="E31" s="5" t="s">
         <v>138</v>
       </c>
@@ -2645,7 +2645,7 @@
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
-      <c r="D32" s="61"/>
+      <c r="D32" s="63"/>
       <c r="E32" s="5" t="s">
         <v>135</v>
       </c>
@@ -2659,7 +2659,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="61"/>
+      <c r="D33" s="63"/>
       <c r="E33" s="5" t="s">
         <v>139</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
-      <c r="D34" s="61"/>
+      <c r="D34" s="63"/>
       <c r="E34" s="5" t="s">
         <v>201</v>
       </c>
@@ -2689,7 +2689,7 @@
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
-      <c r="D35" s="61"/>
+      <c r="D35" s="63"/>
       <c r="E35" s="5" t="s">
         <v>202</v>
       </c>
@@ -2701,7 +2701,7 @@
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
-      <c r="D36" s="61"/>
+      <c r="D36" s="63"/>
       <c r="E36" s="5" t="s">
         <v>144</v>
       </c>
@@ -2715,7 +2715,7 @@
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
-      <c r="D37" s="62"/>
+      <c r="D37" s="64"/>
       <c r="E37" s="11" t="s">
         <v>198</v>
       </c>
@@ -2733,7 +2733,7 @@
       <c r="C38" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="60" t="s">
+      <c r="D38" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -2749,7 +2749,7 @@
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
-      <c r="D39" s="61"/>
+      <c r="D39" s="63"/>
       <c r="E39" s="5" t="s">
         <v>138</v>
       </c>
@@ -2763,7 +2763,7 @@
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
-      <c r="D40" s="61"/>
+      <c r="D40" s="63"/>
       <c r="E40" s="5" t="s">
         <v>136</v>
       </c>
@@ -2777,7 +2777,7 @@
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
-      <c r="D41" s="61"/>
+      <c r="D41" s="63"/>
       <c r="E41" s="5" t="s">
         <v>139</v>
       </c>
@@ -2791,7 +2791,7 @@
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="61"/>
+      <c r="D42" s="63"/>
       <c r="E42" s="5" t="s">
         <v>201</v>
       </c>
@@ -2803,7 +2803,7 @@
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
-      <c r="D43" s="61"/>
+      <c r="D43" s="63"/>
       <c r="E43" s="5" t="s">
         <v>202</v>
       </c>
@@ -2815,7 +2815,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
-      <c r="D44" s="61"/>
+      <c r="D44" s="63"/>
       <c r="E44" s="5" t="s">
         <v>197</v>
       </c>
@@ -2827,7 +2827,7 @@
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
-      <c r="D45" s="62"/>
+      <c r="D45" s="64"/>
       <c r="E45" s="11" t="s">
         <v>198</v>
       </c>
@@ -2935,7 +2935,7 @@
       <c r="C52" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="63" t="s">
+      <c r="D52" s="68" t="s">
         <v>22</v>
       </c>
       <c r="E52" s="4" t="s">
@@ -2951,7 +2951,7 @@
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
-      <c r="D53" s="64"/>
+      <c r="D53" s="66"/>
       <c r="E53" s="4" t="s">
         <v>140</v>
       </c>
@@ -2965,7 +2965,7 @@
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
-      <c r="D54" s="64"/>
+      <c r="D54" s="66"/>
       <c r="E54" s="4" t="s">
         <v>144</v>
       </c>
@@ -2977,7 +2977,7 @@
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
-      <c r="D55" s="65"/>
+      <c r="D55" s="67"/>
       <c r="E55" s="11" t="s">
         <v>198</v>
       </c>
@@ -3235,7 +3235,7 @@
       <c r="C73" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D73" s="60" t="s">
+      <c r="D73" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E73" s="5" t="s">
@@ -3251,7 +3251,7 @@
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
-      <c r="D74" s="61"/>
+      <c r="D74" s="63"/>
       <c r="E74" s="5" t="s">
         <v>141</v>
       </c>
@@ -3265,7 +3265,7 @@
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
-      <c r="D75" s="61"/>
+      <c r="D75" s="63"/>
       <c r="E75" s="5" t="s">
         <v>146</v>
       </c>
@@ -3279,7 +3279,7 @@
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
-      <c r="D76" s="61"/>
+      <c r="D76" s="63"/>
       <c r="E76" s="5" t="s">
         <v>142</v>
       </c>
@@ -3293,7 +3293,7 @@
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
-      <c r="D77" s="61"/>
+      <c r="D77" s="63"/>
       <c r="E77" s="5" t="s">
         <v>203</v>
       </c>
@@ -3305,7 +3305,7 @@
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="61"/>
+      <c r="D78" s="63"/>
       <c r="E78" s="5" t="s">
         <v>204</v>
       </c>
@@ -3317,7 +3317,7 @@
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="61"/>
+      <c r="D79" s="63"/>
       <c r="E79" s="11" t="s">
         <v>147</v>
       </c>
@@ -3331,7 +3331,7 @@
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
-      <c r="D80" s="62"/>
+      <c r="D80" s="64"/>
       <c r="E80" s="5" t="s">
         <v>205</v>
       </c>
@@ -3347,7 +3347,7 @@
       <c r="C81" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D81" s="60" t="s">
+      <c r="D81" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E81" s="5" t="s">
@@ -3361,7 +3361,7 @@
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
-      <c r="D82" s="61"/>
+      <c r="D82" s="63"/>
       <c r="E82" s="5" t="s">
         <v>141</v>
       </c>
@@ -3373,7 +3373,7 @@
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
-      <c r="D83" s="61"/>
+      <c r="D83" s="63"/>
       <c r="E83" s="5" t="s">
         <v>136</v>
       </c>
@@ -3385,7 +3385,7 @@
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="61"/>
+      <c r="D84" s="63"/>
       <c r="E84" s="5" t="s">
         <v>142</v>
       </c>
@@ -3397,7 +3397,7 @@
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
-      <c r="D85" s="61"/>
+      <c r="D85" s="63"/>
       <c r="E85" s="5" t="s">
         <v>203</v>
       </c>
@@ -3411,7 +3411,7 @@
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
-      <c r="D86" s="61"/>
+      <c r="D86" s="63"/>
       <c r="E86" s="5" t="s">
         <v>204</v>
       </c>
@@ -3423,7 +3423,7 @@
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
-      <c r="D87" s="61"/>
+      <c r="D87" s="63"/>
       <c r="E87" s="11" t="s">
         <v>147</v>
       </c>
@@ -3435,7 +3435,7 @@
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
-      <c r="D88" s="62"/>
+      <c r="D88" s="64"/>
       <c r="E88" s="5" t="s">
         <v>205</v>
       </c>
@@ -3537,7 +3537,7 @@
       <c r="C95" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="63" t="s">
+      <c r="D95" s="68" t="s">
         <v>22</v>
       </c>
       <c r="E95" s="4" t="s">
@@ -3553,7 +3553,7 @@
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
-      <c r="D96" s="64"/>
+      <c r="D96" s="66"/>
       <c r="E96" s="4" t="s">
         <v>143</v>
       </c>
@@ -3565,7 +3565,7 @@
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
-      <c r="D97" s="64"/>
+      <c r="D97" s="66"/>
       <c r="E97" s="11" t="s">
         <v>147</v>
       </c>
@@ -3577,7 +3577,7 @@
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
-      <c r="D98" s="65"/>
+      <c r="D98" s="67"/>
       <c r="E98" s="5" t="s">
         <v>205</v>
       </c>
@@ -3817,7 +3817,7 @@
       <c r="C116" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D116" s="60" t="s">
+      <c r="D116" s="62" t="s">
         <v>121</v>
       </c>
       <c r="E116" s="6" t="s">
@@ -3837,7 +3837,7 @@
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
-      <c r="D117" s="61"/>
+      <c r="D117" s="63"/>
       <c r="E117" s="6" t="s">
         <v>30</v>
       </c>
@@ -3855,7 +3855,7 @@
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
-      <c r="D118" s="62"/>
+      <c r="D118" s="64"/>
       <c r="E118" s="6" t="s">
         <v>149</v>
       </c>
@@ -3871,7 +3871,7 @@
       <c r="C119" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D119" s="60" t="s">
+      <c r="D119" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E119" s="6" t="s">
@@ -3885,7 +3885,7 @@
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
-      <c r="D120" s="61"/>
+      <c r="D120" s="63"/>
       <c r="E120" s="6" t="s">
         <v>30</v>
       </c>
@@ -3897,7 +3897,7 @@
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
-      <c r="D121" s="62"/>
+      <c r="D121" s="64"/>
       <c r="E121" s="6" t="s">
         <v>149</v>
       </c>
@@ -4037,7 +4037,7 @@
       <c r="C131" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D131" s="60" t="s">
+      <c r="D131" s="62" t="s">
         <v>121</v>
       </c>
       <c r="E131" s="6" t="s">
@@ -4055,7 +4055,7 @@
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
-      <c r="D132" s="61"/>
+      <c r="D132" s="63"/>
       <c r="E132" s="6" t="s">
         <v>30</v>
       </c>
@@ -4071,7 +4071,7 @@
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
-      <c r="D133" s="62"/>
+      <c r="D133" s="64"/>
       <c r="E133" s="6" t="s">
         <v>149</v>
       </c>
@@ -4087,7 +4087,7 @@
       <c r="C134" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D134" s="60" t="s">
+      <c r="D134" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E134" s="6" t="s">
@@ -4101,7 +4101,7 @@
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
-      <c r="D135" s="61"/>
+      <c r="D135" s="63"/>
       <c r="E135" s="6" t="s">
         <v>30</v>
       </c>
@@ -4113,7 +4113,7 @@
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
-      <c r="D136" s="62"/>
+      <c r="D136" s="64"/>
       <c r="E136" s="6" t="s">
         <v>149</v>
       </c>
@@ -4253,7 +4253,7 @@
       <c r="C146" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D146" s="60" t="s">
+      <c r="D146" s="62" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -4273,7 +4273,7 @@
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
-      <c r="D147" s="61"/>
+      <c r="D147" s="63"/>
       <c r="E147" s="5" t="s">
         <v>34</v>
       </c>
@@ -4289,7 +4289,7 @@
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
-      <c r="D148" s="61"/>
+      <c r="D148" s="63"/>
       <c r="E148" s="5" t="s">
         <v>35</v>
       </c>
@@ -4301,7 +4301,7 @@
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
-      <c r="D149" s="62"/>
+      <c r="D149" s="64"/>
       <c r="E149" s="5" t="s">
         <v>36</v>
       </c>
@@ -4315,7 +4315,7 @@
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D150" s="60" t="s">
+      <c r="D150" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -4329,7 +4329,7 @@
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
-      <c r="D151" s="61"/>
+      <c r="D151" s="63"/>
       <c r="E151" s="5" t="s">
         <v>34</v>
       </c>
@@ -4341,7 +4341,7 @@
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
-      <c r="D152" s="61"/>
+      <c r="D152" s="63"/>
       <c r="E152" s="5" t="s">
         <v>35</v>
       </c>
@@ -4353,7 +4353,7 @@
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
-      <c r="D153" s="62"/>
+      <c r="D153" s="64"/>
       <c r="E153" s="5" t="s">
         <v>36</v>
       </c>
@@ -4409,7 +4409,7 @@
       <c r="C157" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D157" s="60" t="s">
+      <c r="D157" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -4423,7 +4423,7 @@
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
-      <c r="D158" s="61"/>
+      <c r="D158" s="63"/>
       <c r="E158" s="5" t="s">
         <v>35</v>
       </c>
@@ -4435,7 +4435,7 @@
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
-      <c r="D159" s="62"/>
+      <c r="D159" s="64"/>
       <c r="E159" s="5" t="s">
         <v>36</v>
       </c>
@@ -4673,7 +4673,7 @@
       <c r="C176" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D176" s="60" t="s">
+      <c r="D176" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E176" s="6" t="s">
@@ -4689,7 +4689,7 @@
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
-      <c r="D177" s="61"/>
+      <c r="D177" s="63"/>
       <c r="E177" s="6" t="s">
         <v>43</v>
       </c>
@@ -4703,7 +4703,7 @@
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
-      <c r="D178" s="62"/>
+      <c r="D178" s="64"/>
       <c r="E178" s="6" t="s">
         <v>150</v>
       </c>
@@ -4719,7 +4719,7 @@
       <c r="C179" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="60" t="s">
+      <c r="D179" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E179" s="6" t="s">
@@ -4733,7 +4733,7 @@
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
-      <c r="D180" s="61"/>
+      <c r="D180" s="63"/>
       <c r="E180" s="6" t="s">
         <v>43</v>
       </c>
@@ -4745,7 +4745,7 @@
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
-      <c r="D181" s="62"/>
+      <c r="D181" s="64"/>
       <c r="E181" s="6" t="s">
         <v>150</v>
       </c>
@@ -4889,7 +4889,7 @@
       <c r="C191" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D191" s="60" t="s">
+      <c r="D191" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E191" s="6" t="s">
@@ -4905,7 +4905,7 @@
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
-      <c r="D192" s="61"/>
+      <c r="D192" s="63"/>
       <c r="E192" s="6" t="s">
         <v>50</v>
       </c>
@@ -4919,7 +4919,7 @@
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
-      <c r="D193" s="61"/>
+      <c r="D193" s="63"/>
       <c r="E193" s="6" t="s">
         <v>45</v>
       </c>
@@ -4933,7 +4933,7 @@
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
-      <c r="D194" s="61"/>
+      <c r="D194" s="63"/>
       <c r="E194" s="6" t="s">
         <v>46</v>
       </c>
@@ -4947,7 +4947,7 @@
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
-      <c r="D195" s="61"/>
+      <c r="D195" s="63"/>
       <c r="E195" s="11" t="s">
         <v>48</v>
       </c>
@@ -4963,7 +4963,7 @@
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
-      <c r="D196" s="62"/>
+      <c r="D196" s="64"/>
       <c r="E196" s="6" t="s">
         <v>47</v>
       </c>
@@ -4981,7 +4981,7 @@
       <c r="C197" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D197" s="60" t="s">
+      <c r="D197" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E197" s="6" t="s">
@@ -4995,7 +4995,7 @@
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
-      <c r="D198" s="61"/>
+      <c r="D198" s="63"/>
       <c r="E198" s="6" t="s">
         <v>50</v>
       </c>
@@ -5007,7 +5007,7 @@
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
-      <c r="D199" s="61"/>
+      <c r="D199" s="63"/>
       <c r="E199" s="6" t="s">
         <v>151</v>
       </c>
@@ -5019,7 +5019,7 @@
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
-      <c r="D200" s="61"/>
+      <c r="D200" s="63"/>
       <c r="E200" s="6" t="s">
         <v>45</v>
       </c>
@@ -5031,7 +5031,7 @@
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
-      <c r="D201" s="61"/>
+      <c r="D201" s="63"/>
       <c r="E201" s="6" t="s">
         <v>46</v>
       </c>
@@ -5043,7 +5043,7 @@
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
-      <c r="D202" s="61"/>
+      <c r="D202" s="63"/>
       <c r="E202" s="11" t="s">
         <v>156</v>
       </c>
@@ -5057,7 +5057,7 @@
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
-      <c r="D203" s="62"/>
+      <c r="D203" s="64"/>
       <c r="E203" s="6" t="s">
         <v>47</v>
       </c>
@@ -5151,7 +5151,7 @@
       <c r="C209" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D209" s="60" t="s">
+      <c r="D209" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E209" s="6" t="s">
@@ -5165,7 +5165,7 @@
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
-      <c r="D210" s="61"/>
+      <c r="D210" s="63"/>
       <c r="E210" s="6" t="s">
         <v>45</v>
       </c>
@@ -5177,7 +5177,7 @@
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
-      <c r="D211" s="61"/>
+      <c r="D211" s="63"/>
       <c r="E211" s="6" t="s">
         <v>46</v>
       </c>
@@ -5189,7 +5189,7 @@
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
-      <c r="D212" s="61"/>
+      <c r="D212" s="63"/>
       <c r="E212" s="11" t="s">
         <v>156</v>
       </c>
@@ -5203,7 +5203,7 @@
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
-      <c r="D213" s="62"/>
+      <c r="D213" s="64"/>
       <c r="E213" s="6" t="s">
         <v>47</v>
       </c>
@@ -5401,7 +5401,7 @@
       <c r="C227" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D227" s="60" t="s">
+      <c r="D227" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
@@ -5417,7 +5417,7 @@
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
-      <c r="D228" s="61"/>
+      <c r="D228" s="63"/>
       <c r="E228" s="6" t="s">
         <v>54</v>
       </c>
@@ -5431,7 +5431,7 @@
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
-      <c r="D229" s="61"/>
+      <c r="D229" s="63"/>
       <c r="E229" s="6" t="s">
         <v>152</v>
       </c>
@@ -5445,7 +5445,7 @@
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
-      <c r="D230" s="61"/>
+      <c r="D230" s="63"/>
       <c r="E230" s="6" t="s">
         <v>55</v>
       </c>
@@ -5459,7 +5459,7 @@
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
-      <c r="D231" s="61"/>
+      <c r="D231" s="63"/>
       <c r="E231" s="6" t="s">
         <v>56</v>
       </c>
@@ -5473,7 +5473,7 @@
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
-      <c r="D232" s="61"/>
+      <c r="D232" s="63"/>
       <c r="E232" s="11" t="s">
         <v>160</v>
       </c>
@@ -5487,7 +5487,7 @@
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
-      <c r="D233" s="62"/>
+      <c r="D233" s="64"/>
       <c r="E233" s="6" t="s">
         <v>47</v>
       </c>
@@ -5503,7 +5503,7 @@
       <c r="C234" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D234" s="60" t="s">
+      <c r="D234" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E234" s="6" t="s">
@@ -5517,7 +5517,7 @@
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
-      <c r="D235" s="61"/>
+      <c r="D235" s="63"/>
       <c r="E235" s="6" t="s">
         <v>54</v>
       </c>
@@ -5529,7 +5529,7 @@
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
-      <c r="D236" s="61"/>
+      <c r="D236" s="63"/>
       <c r="E236" s="6" t="s">
         <v>152</v>
       </c>
@@ -5541,7 +5541,7 @@
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
-      <c r="D237" s="61"/>
+      <c r="D237" s="63"/>
       <c r="E237" s="6" t="s">
         <v>55</v>
       </c>
@@ -5553,7 +5553,7 @@
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
-      <c r="D238" s="61"/>
+      <c r="D238" s="63"/>
       <c r="E238" s="6" t="s">
         <v>56</v>
       </c>
@@ -5565,7 +5565,7 @@
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
-      <c r="D239" s="61"/>
+      <c r="D239" s="63"/>
       <c r="E239" s="11" t="s">
         <v>160</v>
       </c>
@@ -5577,7 +5577,7 @@
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
-      <c r="D240" s="62"/>
+      <c r="D240" s="64"/>
       <c r="E240" s="6" t="s">
         <v>47</v>
       </c>
@@ -5667,7 +5667,7 @@
       <c r="C246" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D246" s="60" t="s">
+      <c r="D246" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E246" s="6" t="s">
@@ -5681,7 +5681,7 @@
       <c r="A247" s="4"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
-      <c r="D247" s="61"/>
+      <c r="D247" s="63"/>
       <c r="E247" s="6" t="s">
         <v>55</v>
       </c>
@@ -5693,7 +5693,7 @@
       <c r="A248" s="4"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
-      <c r="D248" s="61"/>
+      <c r="D248" s="63"/>
       <c r="E248" s="6" t="s">
         <v>56</v>
       </c>
@@ -5705,7 +5705,7 @@
       <c r="A249" s="4"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
-      <c r="D249" s="61"/>
+      <c r="D249" s="63"/>
       <c r="E249" s="11" t="s">
         <v>160</v>
       </c>
@@ -5717,7 +5717,7 @@
       <c r="A250" s="4"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
-      <c r="D250" s="62"/>
+      <c r="D250" s="64"/>
       <c r="E250" s="6" t="s">
         <v>47</v>
       </c>
@@ -5931,7 +5931,7 @@
       <c r="C266" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D266" s="60" t="s">
+      <c r="D266" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
@@ -5947,7 +5947,7 @@
       <c r="A267" s="4"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
-      <c r="D267" s="61"/>
+      <c r="D267" s="63"/>
       <c r="E267" s="6" t="s">
         <v>161</v>
       </c>
@@ -5961,7 +5961,7 @@
       <c r="A268" s="4"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
-      <c r="D268" s="61"/>
+      <c r="D268" s="63"/>
       <c r="E268" s="6" t="s">
         <v>192</v>
       </c>
@@ -5975,7 +5975,7 @@
       <c r="A269" s="4"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
-      <c r="D269" s="61"/>
+      <c r="D269" s="63"/>
       <c r="E269" s="6" t="s">
         <v>162</v>
       </c>
@@ -5989,7 +5989,7 @@
       <c r="A270" s="4"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
-      <c r="D270" s="61"/>
+      <c r="D270" s="63"/>
       <c r="E270" s="6" t="s">
         <v>163</v>
       </c>
@@ -6003,7 +6003,7 @@
       <c r="A271" s="4"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
-      <c r="D271" s="61"/>
+      <c r="D271" s="63"/>
       <c r="E271" s="11" t="s">
         <v>173</v>
       </c>
@@ -6017,7 +6017,7 @@
       <c r="A272" s="4"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
-      <c r="D272" s="62"/>
+      <c r="D272" s="64"/>
       <c r="E272" s="11" t="s">
         <v>47</v>
       </c>
@@ -6033,7 +6033,7 @@
       <c r="C273" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D273" s="60" t="s">
+      <c r="D273" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E273" s="6" t="s">
@@ -6047,7 +6047,7 @@
       <c r="A274" s="4"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
-      <c r="D274" s="61"/>
+      <c r="D274" s="63"/>
       <c r="E274" s="6" t="s">
         <v>161</v>
       </c>
@@ -6059,7 +6059,7 @@
       <c r="A275" s="4"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
-      <c r="D275" s="61"/>
+      <c r="D275" s="63"/>
       <c r="E275" s="6" t="s">
         <v>192</v>
       </c>
@@ -6071,7 +6071,7 @@
       <c r="A276" s="4"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
-      <c r="D276" s="61"/>
+      <c r="D276" s="63"/>
       <c r="E276" s="6" t="s">
         <v>162</v>
       </c>
@@ -6083,7 +6083,7 @@
       <c r="A277" s="4"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
-      <c r="D277" s="61"/>
+      <c r="D277" s="63"/>
       <c r="E277" s="6" t="s">
         <v>163</v>
       </c>
@@ -6095,7 +6095,7 @@
       <c r="A278" s="4"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
-      <c r="D278" s="61"/>
+      <c r="D278" s="63"/>
       <c r="E278" s="11" t="s">
         <v>173</v>
       </c>
@@ -6107,7 +6107,7 @@
       <c r="A279" s="4"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
-      <c r="D279" s="62"/>
+      <c r="D279" s="64"/>
       <c r="E279" s="11" t="s">
         <v>47</v>
       </c>
@@ -6197,7 +6197,7 @@
       <c r="C285" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D285" s="60" t="s">
+      <c r="D285" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E285" s="6" t="s">
@@ -6211,7 +6211,7 @@
       <c r="A286" s="4"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
-      <c r="D286" s="61"/>
+      <c r="D286" s="63"/>
       <c r="E286" s="6" t="s">
         <v>162</v>
       </c>
@@ -6223,7 +6223,7 @@
       <c r="A287" s="4"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
-      <c r="D287" s="61"/>
+      <c r="D287" s="63"/>
       <c r="E287" s="6" t="s">
         <v>163</v>
       </c>
@@ -6235,7 +6235,7 @@
       <c r="A288" s="4"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
-      <c r="D288" s="61"/>
+      <c r="D288" s="63"/>
       <c r="E288" s="11" t="s">
         <v>173</v>
       </c>
@@ -6247,7 +6247,7 @@
       <c r="A289" s="4"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
-      <c r="D289" s="62"/>
+      <c r="D289" s="64"/>
       <c r="E289" s="11" t="s">
         <v>164</v>
       </c>
@@ -6461,7 +6461,7 @@
       <c r="C305" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D305" s="60" t="s">
+      <c r="D305" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E305" s="6" t="s">
@@ -6477,7 +6477,7 @@
       <c r="A306" s="4"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
-      <c r="D306" s="61"/>
+      <c r="D306" s="63"/>
       <c r="E306" s="6" t="s">
         <v>167</v>
       </c>
@@ -6491,7 +6491,7 @@
       <c r="A307" s="4"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
-      <c r="D307" s="61"/>
+      <c r="D307" s="63"/>
       <c r="E307" s="6" t="s">
         <v>193</v>
       </c>
@@ -6505,7 +6505,7 @@
       <c r="A308" s="4"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
-      <c r="D308" s="61"/>
+      <c r="D308" s="63"/>
       <c r="E308" s="6" t="s">
         <v>168</v>
       </c>
@@ -6519,7 +6519,7 @@
       <c r="A309" s="4"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
-      <c r="D309" s="61"/>
+      <c r="D309" s="63"/>
       <c r="E309" s="6" t="s">
         <v>169</v>
       </c>
@@ -6533,7 +6533,7 @@
       <c r="A310" s="4"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
-      <c r="D310" s="61"/>
+      <c r="D310" s="63"/>
       <c r="E310" s="32" t="s">
         <v>170</v>
       </c>
@@ -6547,7 +6547,7 @@
       <c r="A311" s="4"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
-      <c r="D311" s="62"/>
+      <c r="D311" s="64"/>
       <c r="E311" s="6" t="s">
         <v>47</v>
       </c>
@@ -6563,7 +6563,7 @@
       <c r="C312" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D312" s="60" t="s">
+      <c r="D312" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E312" s="6" t="s">
@@ -6577,7 +6577,7 @@
       <c r="A313" s="4"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
-      <c r="D313" s="61"/>
+      <c r="D313" s="63"/>
       <c r="E313" s="6" t="s">
         <v>167</v>
       </c>
@@ -6589,7 +6589,7 @@
       <c r="A314" s="4"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
-      <c r="D314" s="61"/>
+      <c r="D314" s="63"/>
       <c r="E314" s="6" t="s">
         <v>193</v>
       </c>
@@ -6601,7 +6601,7 @@
       <c r="A315" s="4"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
-      <c r="D315" s="61"/>
+      <c r="D315" s="63"/>
       <c r="E315" s="6" t="s">
         <v>168</v>
       </c>
@@ -6613,7 +6613,7 @@
       <c r="A316" s="4"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
-      <c r="D316" s="61"/>
+      <c r="D316" s="63"/>
       <c r="E316" s="6" t="s">
         <v>169</v>
       </c>
@@ -6625,7 +6625,7 @@
       <c r="A317" s="4"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
-      <c r="D317" s="61"/>
+      <c r="D317" s="63"/>
       <c r="E317" s="32" t="s">
         <v>170</v>
       </c>
@@ -6637,7 +6637,7 @@
       <c r="A318" s="4"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
-      <c r="D318" s="62"/>
+      <c r="D318" s="64"/>
       <c r="E318" s="6" t="s">
         <v>47</v>
       </c>
@@ -6727,7 +6727,7 @@
       <c r="C324" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D324" s="60" t="s">
+      <c r="D324" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E324" s="6" t="s">
@@ -6741,7 +6741,7 @@
       <c r="A325" s="4"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
-      <c r="D325" s="61"/>
+      <c r="D325" s="63"/>
       <c r="E325" s="6" t="s">
         <v>168</v>
       </c>
@@ -6753,7 +6753,7 @@
       <c r="A326" s="4"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
-      <c r="D326" s="61"/>
+      <c r="D326" s="63"/>
       <c r="E326" s="6" t="s">
         <v>169</v>
       </c>
@@ -6765,7 +6765,7 @@
       <c r="A327" s="4"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
-      <c r="D327" s="61"/>
+      <c r="D327" s="63"/>
       <c r="E327" s="32" t="s">
         <v>170</v>
       </c>
@@ -6777,7 +6777,7 @@
       <c r="A328" s="4"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
-      <c r="D328" s="62"/>
+      <c r="D328" s="64"/>
       <c r="E328" s="6" t="s">
         <v>47</v>
       </c>
@@ -6985,7 +6985,7 @@
     </row>
     <row r="344" spans="1:9" s="9" customFormat="1">
       <c r="A344" s="8"/>
-      <c r="B344" s="66" t="s">
+      <c r="B344" s="65" t="s">
         <v>105</v>
       </c>
       <c r="C344" s="8"/>
@@ -7001,7 +7001,7 @@
     </row>
     <row r="345" spans="1:9" s="9" customFormat="1">
       <c r="A345" s="8"/>
-      <c r="B345" s="64"/>
+      <c r="B345" s="66"/>
       <c r="C345" s="8"/>
       <c r="D345" s="8"/>
       <c r="E345" s="8" t="s">
@@ -7013,7 +7013,7 @@
     </row>
     <row r="346" spans="1:9" s="9" customFormat="1">
       <c r="A346" s="8"/>
-      <c r="B346" s="64"/>
+      <c r="B346" s="66"/>
       <c r="C346" s="8"/>
       <c r="D346" s="8"/>
       <c r="E346" s="8" t="s">
@@ -7025,7 +7025,7 @@
     </row>
     <row r="347" spans="1:9" s="9" customFormat="1">
       <c r="A347" s="8"/>
-      <c r="B347" s="64"/>
+      <c r="B347" s="66"/>
       <c r="C347" s="8"/>
       <c r="D347" s="8"/>
       <c r="E347" s="8" t="s">
@@ -7037,7 +7037,7 @@
     </row>
     <row r="348" spans="1:9" s="9" customFormat="1">
       <c r="A348" s="8"/>
-      <c r="B348" s="64"/>
+      <c r="B348" s="66"/>
       <c r="C348" s="8"/>
       <c r="D348" s="8"/>
       <c r="E348" s="8" t="s">
@@ -7049,7 +7049,7 @@
     </row>
     <row r="349" spans="1:9" s="9" customFormat="1">
       <c r="A349" s="8"/>
-      <c r="B349" s="64"/>
+      <c r="B349" s="66"/>
       <c r="C349" s="8"/>
       <c r="D349" s="8"/>
       <c r="E349" s="8" t="s">
@@ -7061,7 +7061,7 @@
     </row>
     <row r="350" spans="1:9" s="9" customFormat="1">
       <c r="A350" s="8"/>
-      <c r="B350" s="65"/>
+      <c r="B350" s="67"/>
       <c r="C350" s="8"/>
       <c r="D350" s="8"/>
       <c r="E350" s="8" t="s">
@@ -7091,7 +7091,7 @@
       <c r="C352" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D352" s="60" t="s">
+      <c r="D352" s="62" t="s">
         <v>16</v>
       </c>
       <c r="E352" s="6" t="s">
@@ -7107,7 +7107,7 @@
       <c r="A353" s="4"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
-      <c r="D353" s="61"/>
+      <c r="D353" s="63"/>
       <c r="E353" s="6" t="s">
         <v>62</v>
       </c>
@@ -7121,7 +7121,7 @@
       <c r="A354" s="4"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
-      <c r="D354" s="61"/>
+      <c r="D354" s="63"/>
       <c r="E354" s="6" t="s">
         <v>63</v>
       </c>
@@ -7135,7 +7135,7 @@
       <c r="A355" s="4"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
-      <c r="D355" s="62"/>
+      <c r="D355" s="64"/>
       <c r="E355" s="11" t="s">
         <v>64</v>
       </c>
@@ -7151,7 +7151,7 @@
       <c r="C356" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D356" s="60" t="s">
+      <c r="D356" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E356" s="6" t="s">
@@ -7165,7 +7165,7 @@
       <c r="A357" s="4"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
-      <c r="D357" s="61"/>
+      <c r="D357" s="63"/>
       <c r="E357" s="6" t="s">
         <v>62</v>
       </c>
@@ -7177,7 +7177,7 @@
       <c r="A358" s="4"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
-      <c r="D358" s="61"/>
+      <c r="D358" s="63"/>
       <c r="E358" s="6" t="s">
         <v>63</v>
       </c>
@@ -7189,7 +7189,7 @@
       <c r="A359" s="4"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
-      <c r="D359" s="62"/>
+      <c r="D359" s="64"/>
       <c r="E359" s="11" t="s">
         <v>64</v>
       </c>
@@ -7249,7 +7249,7 @@
       <c r="C363" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D363" s="60" t="s">
+      <c r="D363" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E363" s="6" t="s">
@@ -7263,7 +7263,7 @@
       <c r="A364" s="4"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
-      <c r="D364" s="61"/>
+      <c r="D364" s="63"/>
       <c r="E364" s="6" t="s">
         <v>63</v>
       </c>
@@ -7275,7 +7275,7 @@
       <c r="A365" s="4"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
-      <c r="D365" s="62"/>
+      <c r="D365" s="64"/>
       <c r="E365" s="11" t="s">
         <v>64</v>
       </c>
@@ -7423,7 +7423,7 @@
       <c r="C375" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D375" s="60" t="s">
+      <c r="D375" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E375" s="6" t="s">
@@ -7439,7 +7439,7 @@
       <c r="A376" s="4"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
-      <c r="D376" s="61"/>
+      <c r="D376" s="63"/>
       <c r="E376" s="6" t="s">
         <v>68</v>
       </c>
@@ -7455,7 +7455,7 @@
       <c r="A377" s="4"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
-      <c r="D377" s="62"/>
+      <c r="D377" s="64"/>
       <c r="E377" s="33" t="s">
         <v>149</v>
       </c>
@@ -7469,7 +7469,7 @@
       <c r="C378" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D378" s="60" t="s">
+      <c r="D378" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E378" s="6" t="s">
@@ -7483,7 +7483,7 @@
       <c r="A379" s="4"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
-      <c r="D379" s="61"/>
+      <c r="D379" s="63"/>
       <c r="E379" s="6" t="s">
         <v>68</v>
       </c>
@@ -7495,7 +7495,7 @@
       <c r="A380" s="4"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
-      <c r="D380" s="62"/>
+      <c r="D380" s="64"/>
       <c r="E380" s="33" t="s">
         <v>149</v>
       </c>
@@ -7539,7 +7539,7 @@
       <c r="C383" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D383" s="60" t="s">
+      <c r="D383" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E383" s="6" t="s">
@@ -7553,7 +7553,7 @@
       <c r="A384" s="4"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
-      <c r="D384" s="62"/>
+      <c r="D384" s="64"/>
       <c r="E384" s="6" t="s">
         <v>153</v>
       </c>
@@ -7657,7 +7657,7 @@
       <c r="C392" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D392" s="60" t="s">
+      <c r="D392" s="62" t="s">
         <v>15</v>
       </c>
       <c r="E392" s="6" t="s">
@@ -7673,7 +7673,7 @@
       <c r="A393" s="4"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
-      <c r="D393" s="61"/>
+      <c r="D393" s="63"/>
       <c r="E393" s="6" t="s">
         <v>70</v>
       </c>
@@ -7689,7 +7689,7 @@
       <c r="A394" s="4"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
-      <c r="D394" s="62"/>
+      <c r="D394" s="64"/>
       <c r="E394" s="33" t="s">
         <v>149</v>
       </c>
@@ -7703,7 +7703,7 @@
       <c r="C395" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D395" s="60" t="s">
+      <c r="D395" s="62" t="s">
         <v>21</v>
       </c>
       <c r="E395" s="6" t="s">
@@ -7717,7 +7717,7 @@
       <c r="A396" s="4"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
-      <c r="D396" s="61"/>
+      <c r="D396" s="63"/>
       <c r="E396" s="6" t="s">
         <v>70</v>
       </c>
@@ -7729,7 +7729,7 @@
       <c r="A397" s="4"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
-      <c r="D397" s="62"/>
+      <c r="D397" s="64"/>
       <c r="E397" s="33" t="s">
         <v>149</v>
       </c>
@@ -7773,7 +7773,7 @@
       <c r="C400" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D400" s="60" t="s">
+      <c r="D400" s="62" t="s">
         <v>22</v>
       </c>
       <c r="E400" s="6" t="s">
@@ -7787,7 +7787,7 @@
       <c r="A401" s="4"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
-      <c r="D401" s="62"/>
+      <c r="D401" s="64"/>
       <c r="E401" s="6" t="s">
         <v>154</v>
       </c>
@@ -7968,6 +7968,35 @@
   </sheetData>
   <autoFilter ref="A1:G414"/>
   <mergeCells count="40">
+    <mergeCell ref="D3:D7"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D116:D118"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="D30:D37"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D73:D80"/>
+    <mergeCell ref="D81:D88"/>
+    <mergeCell ref="D95:D98"/>
+    <mergeCell ref="D157:D159"/>
+    <mergeCell ref="D176:D178"/>
+    <mergeCell ref="D179:D181"/>
+    <mergeCell ref="D197:D203"/>
+    <mergeCell ref="D131:D133"/>
+    <mergeCell ref="D134:D136"/>
+    <mergeCell ref="D146:D149"/>
+    <mergeCell ref="D150:D153"/>
+    <mergeCell ref="D400:D401"/>
+    <mergeCell ref="B344:B350"/>
+    <mergeCell ref="D352:D355"/>
+    <mergeCell ref="D356:D359"/>
+    <mergeCell ref="D363:D365"/>
+    <mergeCell ref="D375:D377"/>
+    <mergeCell ref="D378:D380"/>
+    <mergeCell ref="D383:D384"/>
+    <mergeCell ref="D392:D394"/>
+    <mergeCell ref="D395:D397"/>
     <mergeCell ref="D324:D328"/>
     <mergeCell ref="D209:D213"/>
     <mergeCell ref="D191:D196"/>
@@ -7979,35 +8008,6 @@
     <mergeCell ref="D285:D289"/>
     <mergeCell ref="D305:D311"/>
     <mergeCell ref="D312:D318"/>
-    <mergeCell ref="D400:D401"/>
-    <mergeCell ref="B344:B350"/>
-    <mergeCell ref="D352:D355"/>
-    <mergeCell ref="D356:D359"/>
-    <mergeCell ref="D363:D365"/>
-    <mergeCell ref="D375:D377"/>
-    <mergeCell ref="D378:D380"/>
-    <mergeCell ref="D383:D384"/>
-    <mergeCell ref="D392:D394"/>
-    <mergeCell ref="D395:D397"/>
-    <mergeCell ref="D157:D159"/>
-    <mergeCell ref="D176:D178"/>
-    <mergeCell ref="D179:D181"/>
-    <mergeCell ref="D197:D203"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="D134:D136"/>
-    <mergeCell ref="D146:D149"/>
-    <mergeCell ref="D150:D153"/>
-    <mergeCell ref="D3:D7"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D116:D118"/>
-    <mergeCell ref="D119:D121"/>
-    <mergeCell ref="D30:D37"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D73:D80"/>
-    <mergeCell ref="D81:D88"/>
-    <mergeCell ref="D95:D98"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8022,7 +8022,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="20.5"/>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
     <col min="3" max="4" width="20.5"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
     <col min="6" max="6" width="14.75" customWidth="1"/>
@@ -8176,7 +8176,7 @@
         <v>262</v>
       </c>
       <c r="J5" s="23"/>
-      <c r="M5" s="67" t="s">
+      <c r="M5" s="60" t="s">
         <v>336</v>
       </c>
     </row>
@@ -8282,7 +8282,7 @@
       <c r="F9" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="G9" s="68" t="s">
+      <c r="G9" s="61" t="s">
         <v>361</v>
       </c>
       <c r="H9" s="15" t="s">
@@ -8332,7 +8332,7 @@
       <c r="F11" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="G11" s="68" t="s">
+      <c r="G11" s="61" t="s">
         <v>361</v>
       </c>
       <c r="H11" s="15" t="s">
@@ -8382,7 +8382,7 @@
       <c r="F13" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="G13" s="68" t="s">
+      <c r="G13" s="61" t="s">
         <v>361</v>
       </c>
       <c r="H13" s="15" t="s">
@@ -9218,7 +9218,7 @@
       <c r="F46" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="G46" s="68" t="s">
+      <c r="G46" s="61" t="s">
         <v>361</v>
       </c>
       <c r="H46" s="15" t="s">
@@ -9276,7 +9276,7 @@
       <c r="F48" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="G48" s="68" t="s">
+      <c r="G48" s="61" t="s">
         <v>361</v>
       </c>
       <c r="H48" s="15" t="s">
